--- a/XBRL-template-MPERS/Company/04-SOPL-Nature.xlsx
+++ b/XBRL-template-MPERS/Company/04-SOPL-Nature.xlsx
@@ -644,10 +644,18 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Profit (loss)</t>
-        </is>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>*Profit (loss)</t>
+        </is>
+      </c>
+      <c r="B28">
+        <f>1*B25+1*B27</f>
+        <v/>
+      </c>
+      <c r="C28">
+        <f>1*C25+1*C27</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -685,11 +693,11 @@
         </is>
       </c>
       <c r="B33">
-        <f>1*B25+1*B30+1*B27+1*B31+1*B32</f>
+        <f>1*B30+1*B31+1*B32</f>
         <v/>
       </c>
       <c r="C33">
-        <f>1*C25+1*C30+1*C27+1*C31+1*C32</f>
+        <f>1*C30+1*C31+1*C32</f>
         <v/>
       </c>
     </row>
@@ -1524,11 +1532,11 @@
         </is>
       </c>
       <c r="B104">
-        <f>1*B102+1*B102+1*B103+1*B103</f>
+        <f>1*B102+1*B103</f>
         <v/>
       </c>
       <c r="C104">
-        <f>1*C102+1*C102+1*C103+1*C103</f>
+        <f>1*C102+1*C103</f>
         <v/>
       </c>
     </row>
@@ -1588,11 +1596,11 @@
         </is>
       </c>
       <c r="B112">
-        <f>1*B109+1*B109+1*B110+1*B110+1*B111+1*B111</f>
+        <f>1*B109+1*B110+1*B111</f>
         <v/>
       </c>
       <c r="C112">
-        <f>1*C109+1*C109+1*C110+1*C110+1*C111+1*C111</f>
+        <f>1*C109+1*C110+1*C111</f>
         <v/>
       </c>
     </row>
@@ -1729,11 +1737,11 @@
         </is>
       </c>
       <c r="B131">
-        <f>1*B122+1*B122+1*B123+1*B123+1*B124+1*B124+1*B125+1*B125+1*B126+1*B126+1*B127+1*B127+1*B129+1*B129+1*B128+1*B128+1*B130+1*B130</f>
+        <f>1*B122+1*B123+1*B124+1*B125+1*B126+1*B127+1*B129+1*B128+1*B130</f>
         <v/>
       </c>
       <c r="C131">
-        <f>1*C122+1*C122+1*C123+1*C123+1*C124+1*C124+1*C125+1*C125+1*C126+1*C126+1*C127+1*C127+1*C129+1*C129+1*C128+1*C128+1*C130+1*C130</f>
+        <f>1*C122+1*C123+1*C124+1*C125+1*C126+1*C127+1*C129+1*C128+1*C130</f>
         <v/>
       </c>
     </row>

--- a/XBRL-template-MPERS/Company/04-SOPL-Nature.xlsx
+++ b/XBRL-template-MPERS/Company/04-SOPL-Nature.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -447,257 +447,270 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Disclosure on statement of profit or loss [abstract]</t>
-        </is>
+          <t>Disclosure on statement of profit or loss</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>'SOPL-Analysis-Nature'!B3</f>
+        <v/>
+      </c>
+      <c r="C3">
+        <f>'SOPL-Analysis-Nature'!C3</f>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Statement of Profit or Loss [abstract]</t>
+          <t>Statement of Profit or Loss</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Statement of profit or loss [table]</t>
+          <t>Continuing operations</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Consolidated and separate financial statements [axis]</t>
-        </is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>'SOPL-Analysis-Nature'!B39</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>'SOPL-Analysis-Nature'!C39</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Group [member]</t>
-        </is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>'SOPL-Analysis-Nature'!B81</f>
+        <v/>
+      </c>
+      <c r="C7">
+        <f>'SOPL-Analysis-Nature'!C81</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Company [member]</t>
+          <t>Increase (decrease) in inventories of finished goods and work in progress</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Statement of profit or loss [line items]</t>
+          <t>Raw materials and consumables used</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Continuing operations [abstract]</t>
-        </is>
+          <t>Employee benefits expense</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>'SOPL-Analysis-Nature'!B94</f>
+        <v/>
+      </c>
+      <c r="C10">
+        <f>'SOPL-Analysis-Nature'!C94</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Depreciation and amortisation expense</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
+          <t>Other expenses</t>
+        </is>
+      </c>
+      <c r="B12">
+        <f>'SOPL-Analysis-Nature'!B128</f>
+        <v/>
+      </c>
+      <c r="C12">
+        <f>'SOPL-Analysis-Nature'!C128</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Increase (decrease) in inventories of finished goods and work in progress</t>
-        </is>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>*Profit (loss) from operating activities</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>1*B6+1*B7+-1*B8+-1*B9+-1*B10+-1*B11+-1*B12</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>1*C6+1*C7+-1*C8+-1*C9+-1*C10+-1*C11+-1*C12</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Raw materials and consumables used</t>
-        </is>
+          <t>Finance income</t>
+        </is>
+      </c>
+      <c r="B14">
+        <f>'SOPL-Analysis-Nature'!B132</f>
+        <v/>
+      </c>
+      <c r="C14">
+        <f>'SOPL-Analysis-Nature'!C132</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Employee benefits expense</t>
+          <t>Finance costs</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Depreciation and amortisation expense</t>
+          <t>Share of profit (loss) of associates and joint ventures accounted for using equity method</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Other expenses</t>
-        </is>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>*Profit (loss) before tax</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>1*B6+1*B7+1*B14+-1*B15+1*B16+-1*B8+-1*B9+-1*B10+-1*B11+-1*B12</f>
+        <v/>
+      </c>
+      <c r="C17">
+        <f>1*C6+1*C7+1*C14+-1*C15+1*C16+-1*C8+-1*C9+-1*C10+-1*C11+-1*C12</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>*Profit (loss) from operating activities</t>
-        </is>
-      </c>
-      <c r="B18">
-        <f>1*B11+1*B12+-1*B13+-1*B14+-1*B15+-1*B16+-1*B17</f>
-        <v/>
-      </c>
-      <c r="C18">
-        <f>1*C11+1*C12+-1*C13+-1*C14+-1*C15+-1*C16+-1*C17</f>
-        <v/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Tax expense</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Finance income</t>
+          <t>Contribution to zakat</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Finance costs</t>
-        </is>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>*Profit (loss) from continuing operations</t>
+        </is>
+      </c>
+      <c r="B20">
+        <f>1*B17+-1*B18+-1*B19</f>
+        <v/>
+      </c>
+      <c r="C20">
+        <f>1*C17+-1*C18+-1*C19</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Share of profit (loss) of associates and joint ventures accounted for using equity method</t>
+          <t>Discontinued operations</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>*Profit (loss) before tax</t>
-        </is>
-      </c>
-      <c r="B22">
-        <f>1*B11+1*B12+1*B19+-1*B20+1*B21+-1*B13+-1*B14+-1*B15+-1*B16+-1*B17</f>
-        <v/>
-      </c>
-      <c r="C22">
-        <f>1*C11+1*C12+1*C19+-1*C20+1*C21+-1*C13+-1*C14+-1*C15+-1*C16+-1*C17</f>
-        <v/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Profit (loss) before tax, from discontinued operation</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Tax expense</t>
-        </is>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>*Profit (loss)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <f>1*B20+1*B22</f>
+        <v/>
+      </c>
+      <c r="C23">
+        <f>1*C20+1*C22</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Contribution to zakat</t>
+          <t>Profit (loss), attributable to</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>*Profit (loss) from continuing operations</t>
-        </is>
-      </c>
-      <c r="B25">
-        <f>1*B22+-1*B23+-1*B24</f>
-        <v/>
-      </c>
-      <c r="C25">
-        <f>1*C22+-1*C23+-1*C24</f>
-        <v/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Profit (loss), attributable to owners of parent</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Discontinued operations [abstract]</t>
+          <t>Profit (loss), attributable to equity other components</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Profit (loss) before tax, from discontinued operation</t>
+          <t>Profit (loss), attributable to non-controlling interests</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>*Profit (loss)</t>
+          <t>*Total Profit (Loss)</t>
         </is>
       </c>
       <c r="B28">
-        <f>1*B25+1*B27</f>
+        <f>1*B25+1*B26+1*B27</f>
         <v/>
       </c>
       <c r="C28">
-        <f>1*C25+1*C27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Profit (loss), attributable to [abstract]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Profit (loss), attributable to owners of parent</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Profit (loss), attributable to equity other components</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Profit (loss), attributable to non-controlling interests</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>*Total Profit (Loss)</t>
-        </is>
-      </c>
-      <c r="B33">
-        <f>1*B30+1*B31+1*B32</f>
-        <v/>
-      </c>
-      <c r="C33">
-        <f>1*C30+1*C31+1*C32</f>
+        <f>1*C25+1*C26+1*C27</f>
         <v/>
       </c>
     </row>
@@ -712,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -741,1065 +754,1030 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Disclosure on statement of profit or loss [abstract]</t>
+          <t>Disclosure on statement of profit or loss</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Analysis of profit or loss [abstract]</t>
+          <t>Analysis of profit or loss</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Statement of profit or loss [table]</t>
+          <t>Revenue</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Consolidated and separate financial statements [axis]</t>
+          <t>Revenue from sale of goods</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Group [member]</t>
+          <t>Revenue from sale of broadband and telecommunication</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Company [member]</t>
+          <t>Revenue from property development</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Statement of profit or loss [line items]</t>
+          <t>Revenue from construction contracts</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Revenue [abstract]</t>
+          <t>Sale of clean water, treatment and disposal of waste water</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Revenue from sale of goods [abstract]</t>
+          <t>Revenue from sale of food and beverage</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Revenue from sale of broadband and telecommunication</t>
+          <t>Revenue from sale of agricultural produce</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Revenue from property development</t>
+          <t>Revenue from sale of oil and gas products</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Revenue from construction contracts</t>
+          <t>Other revenue from sale of goods</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Sale of clean water, treatment and disposal of waste water</t>
-        </is>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>*Total revenue from sale of goods</t>
+        </is>
+      </c>
+      <c r="B15">
+        <f>1*B7+1*B8+1*B9+1*B10+1*B11+1*B12+1*B13+1*B14</f>
+        <v/>
+      </c>
+      <c r="C15">
+        <f>1*C7+1*C8+1*C9+1*C10+1*C11+1*C12+1*C13+1*C14</f>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Revenue from sale of food and beverage</t>
+          <t>Revenue from rendering of services</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Revenue from sale of agricultural produce</t>
+          <t>Income from entertainment operations</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Revenue from sale of oil and gas products</t>
+          <t>Revenue from rendering of telecommunication services</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Other revenue from sale of goods</t>
+          <t>Revenue from rendering of transportation services</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>*Total revenue from sale of goods</t>
-        </is>
-      </c>
-      <c r="B20">
-        <f>1*B12+1*B13+1*B14+1*B15+1*B16+1*B17+1*B18+1*B19</f>
-        <v/>
-      </c>
-      <c r="C20">
-        <f>1*C12+1*C13+1*C14+1*C15+1*C16+1*C17+1*C18+1*C19</f>
-        <v/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Revenue from rendering of information technology services</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Revenue from rendering of services [abstract]</t>
+          <t>Education services income</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Income from entertainment operations</t>
+          <t>Healthcare services income</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Revenue from rendering of telecommunication services</t>
+          <t>Revenue from rendering of shipping and shipping related services</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Revenue from rendering of transportation services</t>
+          <t>Other revenue from rendering of services</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Revenue from rendering of information technology services</t>
-        </is>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>*Total revenue from rendering of services</t>
+        </is>
+      </c>
+      <c r="B25">
+        <f>1*B17+1*B18+1*B19+1*B20+1*B21+1*B22+1*B23+1*B24</f>
+        <v/>
+      </c>
+      <c r="C25">
+        <f>1*C17+1*C18+1*C19+1*C20+1*C21+1*C22+1*C23+1*C24</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Education services income</t>
+          <t>Interest income</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Healthcare services income</t>
+          <t>Interest income on loans, advances and financing</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Revenue from rendering of shipping and shipping related services</t>
+          <t>Interest income on other financial assets</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Other revenue from rendering of services</t>
-        </is>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>*Total interest income</t>
+        </is>
+      </c>
+      <c r="B29">
+        <f>1*B27+1*B28</f>
+        <v/>
+      </c>
+      <c r="C29">
+        <f>1*C27+1*C28</f>
+        <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>*Total revenue from rendering of services</t>
-        </is>
-      </c>
-      <c r="B30">
-        <f>1*B22+1*B23+1*B24+1*B25+1*B26+1*B27+1*B28+1*B29</f>
-        <v/>
-      </c>
-      <c r="C30">
-        <f>1*C22+1*C23+1*C24+1*C25+1*C26+1*C27+1*C28+1*C29</f>
-        <v/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Other fee and commission income</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Interest income [abstract]</t>
+          <t>Gross brokerage and other charges</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Interest income on loans, advances and financing</t>
+          <t>Underwriting commissions and fund management income</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Interest income on other financial assets</t>
+          <t>Other fee and commission</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>*Total interest income</t>
+          <t>*Total other fee and commission income</t>
         </is>
       </c>
       <c r="B34">
-        <f>1*B32+1*B33</f>
+        <f>1*B31+1*B32+1*B33</f>
         <v/>
       </c>
       <c r="C34">
-        <f>1*C32+1*C33</f>
+        <f>1*C31+1*C32+1*C33</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Other fee and commission income [abstract]</t>
+          <t>Dividend income</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Gross brokerage and other charges</t>
+          <t>Rental income</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Underwriting commissions and fund management income</t>
+          <t>Royalty income</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Other fee and commission</t>
+          <t>Other revenue</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>*Total other fee and commission income</t>
+          <t>*Total revenue</t>
         </is>
       </c>
       <c r="B39">
-        <f>1*B36+1*B37+1*B38</f>
+        <f>1*B15+1*B25+1*B29+1*B34+1*B35+1*B36+1*B37+1*B38</f>
         <v/>
       </c>
       <c r="C39">
-        <f>1*C36+1*C37+1*C38</f>
+        <f>1*C15+1*C25+1*C29+1*C34+1*C35+1*C36+1*C37+1*C38</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dividend income</t>
+          <t>Other income</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Rental income</t>
+          <t>Deferred income</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Royalty income</t>
+          <t>Bad debts recovered</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Other revenue</t>
+          <t>Dividend, other income</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>*Total revenue</t>
-        </is>
-      </c>
-      <c r="B44">
-        <f>1*B20+1*B30+1*B34+1*B39+1*B40+1*B41+1*B42+1*B43</f>
-        <v/>
-      </c>
-      <c r="C44">
-        <f>1*C20+1*C30+1*C34+1*C39+1*C40+1*C41+1*C42+1*C43</f>
-        <v/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Other income [abstract]</t>
+          <t>Realised foreign currencies exchange gain transferred from equity</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Deferred income</t>
+          <t>Unrealised gain on foreign exchange</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Bad debts recovered</t>
-        </is>
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>*Total foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="B47">
+        <f>1*B45+1*B46</f>
+        <v/>
+      </c>
+      <c r="C47">
+        <f>1*C45+1*C46</f>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dividend, other income</t>
+          <t>Gain on disposal of subsidiaries, associates and joint ventures</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Foreign exchange gain [abstract]</t>
+          <t>Gain on disposal of subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Realised foreign currencies exchange gain transferred from equity</t>
+          <t>Gain on disposal of associates</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Unrealised gain on foreign exchange</t>
+          <t>Gain on disposal of joint ventures</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>*Total foreign exchange gain</t>
+          <t>*Total gain on disposal of subsidiaries, associates and joint ventures</t>
         </is>
       </c>
       <c r="B52">
-        <f>1*B50+1*B51</f>
+        <f>1*B49+1*B50+1*B51</f>
         <v/>
       </c>
       <c r="C52">
-        <f>1*C50+1*C51</f>
+        <f>1*C49+1*C50+1*C51</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Gain on disposal of subsidiaries, associates and joint ventures [abstract]</t>
+          <t>Gain on disposal from other investments</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Gain on disposal of subsidiaries</t>
+          <t>Gain on disposals of property, plant and equipment</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Gain on disposal of associates</t>
+          <t>Gains on disposal of other non-current assets</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Gain on disposal of joint ventures</t>
+          <t>Gain on revaluation</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>*Total gain on disposal of subsidiaries, associates and joint ventures</t>
-        </is>
-      </c>
-      <c r="B57">
-        <f>1*B54+1*B55+1*B56</f>
-        <v/>
-      </c>
-      <c r="C57">
-        <f>1*C54+1*C55+1*C56</f>
-        <v/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Gain on disposal from other investments</t>
+          <t>Management fees, other income</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Gain on disposals of property, plant and equipment</t>
+          <t>Net fair value gain on derivatives</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Gains on disposal of other non-current assets</t>
+          <t>Net fair value gain on recycle of forex reserve upon disposal of subsidiaries</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Gain on revaluation</t>
+          <t>Other fee and commission, other income</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Other rental income</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Management fees, other income</t>
+          <t>Rental income on land and buildings</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Net fair value gain on derivatives</t>
+          <t>Reversal of impairment loss recognised in profit or loss</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Net fair value gain on recycle of forex reserve upon disposal of subsidiaries</t>
+          <t>Reversal of impairment loss on receivables</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Other fee and commission, other income</t>
+          <t>(Reversal of)/Impairment loss on inventories</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Other rental income</t>
+          <t>Reversal of impairment loss on intangible assets other than goodwill</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Rental income on land and buildings</t>
+          <t>Reversal of impairment loss on goodwill</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Reversal of impairment loss recognised in profit or loss [abstract]</t>
+          <t>Reversal of impairment loss on property, plant and equipment</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Reversal of impairment loss on receivables</t>
+          <t>Reversal of impairment loss on investment in associates</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>(Reversal of)/Impairment loss on inventories</t>
+          <t>Reversal of impairment loss on investment in joint ventures</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Reversal of impairment loss on intangible assets other than goodwill</t>
+          <t>Reversal of impairment loss on other assets</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Reversal of impairment loss on goodwill</t>
-        </is>
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>*Total reversal of impairment loss recognised in profit or loss</t>
+        </is>
+      </c>
+      <c r="B73">
+        <f>1*B65+1*B66+1*B67+1*B69+1*B70+1*B71+1*B72+1*B68</f>
+        <v/>
+      </c>
+      <c r="C73">
+        <f>1*C65+1*C66+1*C67+1*C69+1*C70+1*C71+1*C72+1*C68</f>
+        <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Reversal of impairment loss on property, plant and equipment</t>
+          <t>Royalty/franchise income</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Reversal of impairment loss on investment in associates</t>
+          <t>Grant or incentives by Malaysian government or it's agencies</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Reversal of impairment loss on investment in joint ventures</t>
+          <t>Grant or incentives by foreign government or it's agencies</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Reversal of impairment loss on other assets</t>
+          <t>Contributions or donations by local contributor</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="inlineStr">
-        <is>
-          <t>*Total reversal of impairment loss recognised in profit or loss</t>
-        </is>
-      </c>
-      <c r="B78">
-        <f>1*B70+1*B71+1*B72+1*B74+1*B75+1*B76+1*B77+1*B73</f>
-        <v/>
-      </c>
-      <c r="C78">
-        <f>1*C70+1*C71+1*C72+1*C74+1*C75+1*C76+1*C77+1*C73</f>
-        <v/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Contributions or donations by foreign contributor</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Royalty/franchise income</t>
+          <t>Contributions or donations by unknown contributor</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Grant or incentives by Malaysian government or it's agencies</t>
+          <t>Miscellaneous other operating income</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Grant or incentives by foreign government or it's agencies</t>
-        </is>
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>*Total other income</t>
+        </is>
+      </c>
+      <c r="B81">
+        <f>1*B41+1*B42+1*B43+1*B47+1*B52+1*B53+1*B54+1*B55+1*B56+1*B57+1*B58+1*B61+1*B62+1*B63+1*B73+1*B74+1*B75+1*B76+1*B77+1*B78+1*B79+1*B80+1*B59+1*B60</f>
+        <v/>
+      </c>
+      <c r="C81">
+        <f>1*C41+1*C42+1*C43+1*C47+1*C52+1*C53+1*C54+1*C55+1*C56+1*C57+1*C58+1*C61+1*C62+1*C63+1*C73+1*C74+1*C75+1*C76+1*C77+1*C78+1*C79+1*C80+1*C59+1*C60</f>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Contributions or donations by local contributor</t>
+          <t>Employee benefits expense</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Contributions or donations by foreign contributor</t>
+          <t>Wages, salaries and others</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Contributions or donations by unknown contributor</t>
+          <t>Bonus</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Miscellaneous other operating income</t>
+          <t>Share-based compensation expense</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="inlineStr">
-        <is>
-          <t>*Total other income</t>
-        </is>
-      </c>
-      <c r="B86">
-        <f>1*B46+1*B47+1*B48+1*B52+1*B57+1*B58+1*B59+1*B60+1*B61+1*B62+1*B63+1*B66+1*B67+1*B68+1*B78+1*B79+1*B80+1*B81+1*B82+1*B83+1*B84+1*B85+1*B64+1*B65</f>
-        <v/>
-      </c>
-      <c r="C86">
-        <f>1*C46+1*C47+1*C48+1*C52+1*C57+1*C58+1*C59+1*C60+1*C61+1*C62+1*C63+1*C66+1*C67+1*C68+1*C78+1*C79+1*C80+1*C81+1*C82+1*C83+1*C84+1*C85+1*C64+1*C65</f>
-        <v/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Share option expenses</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Employee benefits expense [abstract]</t>
+          <t>Social security contributions</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Wages, salaries and others</t>
+          <t>Termination benefits</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Bonus</t>
+          <t>Defined contribution plans</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Share-based compensation expense</t>
+          <t>Defined benefit plans</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Share option expenses</t>
+          <t>Other long-term employee benefits</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Social security contributions</t>
+          <t>Other short-term employee benefits</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Termination benefits</t>
+          <t>Other employee benefit expenses</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Defined contribution plans</t>
-        </is>
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>*Total employee benefits expense</t>
+        </is>
+      </c>
+      <c r="B94">
+        <f>1*B83+1*B84+1*B85+1*B86+1*B87+1*B88+1*B90+1*B89+1*B91+1*B92+1*B93</f>
+        <v/>
+      </c>
+      <c r="C94">
+        <f>1*C83+1*C84+1*C85+1*C86+1*C87+1*C88+1*C90+1*C89+1*C91+1*C92+1*C93</f>
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Defined benefit plans</t>
+          <t>Other expenses</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Other long-term employee benefits</t>
+          <t>Auditor's remuneration</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Other short-term employee benefits</t>
+          <t>Auditor's remuneration for audit services</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Other employee benefit expenses</t>
+          <t>Auditor's remuneration for other services</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>*Total employee benefits expense</t>
+          <t>*Total auditor's remuneration</t>
         </is>
       </c>
       <c r="B99">
-        <f>1*B88+1*B89+1*B90+1*B91+1*B92+1*B93+1*B95+1*B94+1*B96+1*B97+1*B98</f>
+        <f>1*B97+1*B98</f>
         <v/>
       </c>
       <c r="C99">
-        <f>1*C88+1*C89+1*C90+1*C91+1*C92+1*C93+1*C95+1*C94+1*C96+1*C97+1*C98</f>
+        <f>1*C97+1*C98</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Other expenses [abstract]</t>
+          <t>Amortisation expense</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Auditor's remuneration [abstract]</t>
+          <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Auditor's remuneration for audit services</t>
+          <t>Natural disaster related expenses</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Auditor's remuneration for other services</t>
+          <t>Loss on disposal of subsidiaries, associates and joint ventures</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="inlineStr">
-        <is>
-          <t>*Total auditor's remuneration</t>
-        </is>
-      </c>
-      <c r="B104">
-        <f>1*B102+1*B103</f>
-        <v/>
-      </c>
-      <c r="C104">
-        <f>1*C102+1*C103</f>
-        <v/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Loss on disposal of subsidiaries</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Amortisation expense</t>
+          <t>Loss on disposal of associates</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Depreciation of property, plant and equipment</t>
+          <t>Loss on disposal of joint ventures</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Natural disaster related expenses</t>
-        </is>
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>*Total loss on disposal of subsidiaries, associates and joint ventures</t>
+        </is>
+      </c>
+      <c r="B107">
+        <f>1*B104+1*B105+1*B106</f>
+        <v/>
+      </c>
+      <c r="C107">
+        <f>1*C104+1*C105+1*C106</f>
+        <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Loss on disposal of subsidiaries, associates and joint ventures [abstract]</t>
+          <t>Loss on disposal from other investments</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Loss on disposal of subsidiaries</t>
+          <t>Loss on disposal of property, plant and equipment</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Loss on disposal of associates</t>
+          <t>Loss on disposal of other non-current assets</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Loss on disposal of joint ventures</t>
+          <t>Loss on revaluation</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="inlineStr">
-        <is>
-          <t>*Total loss on disposal of subsidiaries, associates and joint ventures</t>
-        </is>
-      </c>
-      <c r="B112">
-        <f>1*B109+1*B110+1*B111</f>
-        <v/>
-      </c>
-      <c r="C112">
-        <f>1*C109+1*C110+1*C111</f>
-        <v/>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Provision for liabilities and charges</t>
+        </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Loss on disposal from other investments</t>
+          <t>Provision of warranties and guarantees</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Loss on disposal of property, plant and equipment</t>
+          <t>Rental expenses</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Loss on disposal of other non-current assets</t>
+          <t>Royalty expenses</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Loss on revaluation</t>
+          <t>Director's remuneration</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Provision for liabilities and charges</t>
+          <t>Salaries and other emoluments</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Provision of warranties and guarantees</t>
+          <t>Bonus</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Rental expenses</t>
+          <t>Share option expenses</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Royalty expenses</t>
+          <t>Benefits-in-kind</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Director's remuneration [abstract]</t>
+          <t>Fees</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Salaries and other emoluments</t>
+          <t>Performance incentives</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Bonus</t>
+          <t>Defined contribution plans</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Share option expenses</t>
+          <t>Defined benefit plans</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Benefits-in-kind</t>
+          <t>Other emoluments</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Fees</t>
-        </is>
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>*Total Director's remuneration</t>
+        </is>
+      </c>
+      <c r="B126">
+        <f>1*B117+1*B118+1*B119+1*B120+1*B121+1*B122+1*B124+1*B123+1*B125</f>
+        <v/>
+      </c>
+      <c r="C126">
+        <f>1*C117+1*C118+1*C119+1*C120+1*C121+1*C122+1*C124+1*C123+1*C125</f>
+        <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Performance incentives</t>
+          <t>Other miscellaneous expenses</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Defined contribution plans</t>
-        </is>
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>*Total other expenses</t>
+        </is>
+      </c>
+      <c r="B128">
+        <f>1*B99+1*B100+1*B101+1*B102+1*B107+1*B108+1*B109+1*B110+1*B111+1*B112+1*B113+1*B114+1*B115+1*B126+1*B127</f>
+        <v/>
+      </c>
+      <c r="C128">
+        <f>1*C99+1*C100+1*C101+1*C102+1*C107+1*C108+1*C109+1*C110+1*C111+1*C112+1*C113+1*C114+1*C115+1*C126+1*C127</f>
+        <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Defined benefit plans</t>
+          <t>Finance income</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Other emoluments</t>
+          <t>Finance income due from related parties</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="inlineStr">
-        <is>
-          <t>*Total Director's remuneration</t>
-        </is>
-      </c>
-      <c r="B131">
-        <f>1*B122+1*B123+1*B124+1*B125+1*B126+1*B127+1*B129+1*B128+1*B130</f>
-        <v/>
-      </c>
-      <c r="C131">
-        <f>1*C122+1*C123+1*C124+1*C125+1*C126+1*C127+1*C129+1*C128+1*C130</f>
-        <v/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Other finance income</t>
+        </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Other miscellaneous expenses</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="1" t="inlineStr">
-        <is>
-          <t>*Total other expenses</t>
-        </is>
-      </c>
-      <c r="B133">
-        <f>1*B104+1*B105+1*B106+1*B107+1*B112+1*B113+1*B114+1*B115+1*B116+1*B117+1*B118+1*B119+1*B120+1*B131+1*B132</f>
-        <v/>
-      </c>
-      <c r="C133">
-        <f>1*C104+1*C105+1*C106+1*C107+1*C112+1*C113+1*C114+1*C115+1*C116+1*C117+1*C118+1*C119+1*C120+1*C131+1*C132</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Finance income [abstract]</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Finance income due from related parties</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Other finance income</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="1" t="inlineStr">
+      <c r="A132" s="1" t="inlineStr">
         <is>
           <t>*Total finance income</t>
         </is>
       </c>
-      <c r="B137">
-        <f>1*B135+1*B136</f>
-        <v/>
-      </c>
-      <c r="C137">
-        <f>1*C135+1*C136</f>
+      <c r="B132">
+        <f>1*B130+1*B131</f>
+        <v/>
+      </c>
+      <c r="C132">
+        <f>1*C130+1*C131</f>
         <v/>
       </c>
     </row>

--- a/XBRL-template-MPERS/Company/04-SOPL-Nature.xlsx
+++ b/XBRL-template-MPERS/Company/04-SOPL-Nature.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,14 +28,24 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF1F3864"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -50,9 +60,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,7 +456,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Disclosure on statement of profit or loss</t>
         </is>
@@ -460,14 +471,14 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Statement of Profit or Loss</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Continuing operations</t>
         </is>
@@ -555,7 +566,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>*Profit (loss) from operating activities</t>
         </is>
@@ -599,7 +610,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>*Profit (loss) before tax</t>
         </is>
@@ -628,7 +639,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>*Profit (loss) from continuing operations</t>
         </is>
@@ -643,7 +654,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>Discontinued operations</t>
         </is>
@@ -657,7 +668,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>*Profit (loss)</t>
         </is>
@@ -672,7 +683,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Profit (loss), attributable to</t>
         </is>
@@ -700,7 +711,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>*Total Profit (Loss)</t>
         </is>
@@ -752,28 +763,28 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Disclosure on statement of profit or loss</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Analysis of profit or loss</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Revenue from sale of goods</t>
         </is>
@@ -836,7 +847,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>*Total revenue from sale of goods</t>
         </is>
@@ -851,7 +862,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Revenue from rendering of services</t>
         </is>
@@ -914,7 +925,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>*Total revenue from rendering of services</t>
         </is>
@@ -929,7 +940,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>Interest income</t>
         </is>
@@ -950,7 +961,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>*Total interest income</t>
         </is>
@@ -965,7 +976,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>Other fee and commission income</t>
         </is>
@@ -993,7 +1004,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>*Total other fee and commission income</t>
         </is>
@@ -1036,7 +1047,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>*Total revenue</t>
         </is>
@@ -1051,7 +1062,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>Other income</t>
         </is>
@@ -1079,7 +1090,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>Foreign exchange gain</t>
         </is>
@@ -1100,7 +1111,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>*Total foreign exchange gain</t>
         </is>
@@ -1115,7 +1126,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>Gain on disposal of subsidiaries, associates and joint ventures</t>
         </is>
@@ -1143,7 +1154,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>*Total gain on disposal of subsidiaries, associates and joint ventures</t>
         </is>
@@ -1235,7 +1246,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="1" t="inlineStr">
         <is>
           <t>Reversal of impairment loss recognised in profit or loss</t>
         </is>
@@ -1298,7 +1309,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>*Total reversal of impairment loss recognised in profit or loss</t>
         </is>
@@ -1362,7 +1373,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>*Total other income</t>
         </is>
@@ -1377,7 +1388,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="1" t="inlineStr">
         <is>
           <t>Employee benefits expense</t>
         </is>
@@ -1461,7 +1472,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>*Total employee benefits expense</t>
         </is>
@@ -1476,14 +1487,14 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="1" t="inlineStr">
         <is>
           <t>Other expenses</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="1" t="inlineStr">
         <is>
           <t>Auditor's remuneration</t>
         </is>
@@ -1504,7 +1515,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="inlineStr">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>*Total auditor's remuneration</t>
         </is>
@@ -1540,7 +1551,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="1" t="inlineStr">
         <is>
           <t>Loss on disposal of subsidiaries, associates and joint ventures</t>
         </is>
@@ -1568,7 +1579,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>*Total loss on disposal of subsidiaries, associates and joint ventures</t>
         </is>
@@ -1639,7 +1650,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="1" t="inlineStr">
         <is>
           <t>Director's remuneration</t>
         </is>
@@ -1709,7 +1720,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>*Total Director's remuneration</t>
         </is>
@@ -1731,7 +1742,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="inlineStr">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>*Total other expenses</t>
         </is>
@@ -1746,7 +1757,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="1" t="inlineStr">
         <is>
           <t>Finance income</t>
         </is>
@@ -1767,7 +1778,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>*Total finance income</t>
         </is>
